--- a/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/miRNA Experiment/GDC_Exp_miRNA_CB.xlsx
+++ b/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/miRNA Experiment/GDC_Exp_miRNA_CB.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjohnson/Projects/SDD-Dataset/data/The-Cancer-Genomic-Atlas/2023-06-29_clean/miRNA Experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97074906-29D4-F04A-8F4B-1C8AF55317BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFECD7C2-05CB-5A4F-B1CB-294AAFF25B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12380" yWindow="8000" windowWidth="27240" windowHeight="16440"/>
+    <workbookView xWindow="1400" yWindow="2600" windowWidth="27240" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GDC_Exp_miRNA_CB" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Dictionary" sheetId="2" r:id="rId1"/>
+    <sheet name="Codebook" sheetId="3" r:id="rId2"/>
+    <sheet name="GDC_Exp_miRNA_CB" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>Column</t>
   </si>
@@ -53,13 +55,118 @@
   </si>
   <si>
     <t>Not cross-mapped</t>
+  </si>
+  <si>
+    <t>VARNAME</t>
+  </si>
+  <si>
+    <t>PRIMARY KEY</t>
+  </si>
+  <si>
+    <t>CHEAR VARIABLE</t>
+  </si>
+  <si>
+    <t>VARDESC</t>
+  </si>
+  <si>
+    <t>QUESTION</t>
+  </si>
+  <si>
+    <t>VARIABLE LOCATION</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>FORMAT</t>
+  </si>
+  <si>
+    <t>UNITS</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>MISSING VALUES</t>
+  </si>
+  <si>
+    <t>DERIVED VARIABLE</t>
+  </si>
+  <si>
+    <t>RESOLUTION</t>
+  </si>
+  <si>
+    <t>COMMENT 1</t>
+  </si>
+  <si>
+    <t>COMMENT 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARNAME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARDESC </t>
+  </si>
+  <si>
+    <t>CODES</t>
+  </si>
+  <si>
+    <t>DEFINITION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCALE: 1=continuous, 2=categorical 3 =ordinal </t>
+  </si>
+  <si>
+    <t>COMMENT</t>
+  </si>
+  <si>
+    <t>Derived variable? 1=yes, 2=no</t>
+  </si>
+  <si>
+    <t>If derived, list source variables</t>
+  </si>
+  <si>
+    <t>miRNA_ID</t>
+  </si>
+  <si>
+    <t>read_count</t>
+  </si>
+  <si>
+    <t>reads_per_million_miRNA_mapped</t>
+  </si>
+  <si>
+    <t>The subject's gene identifier</t>
+  </si>
+  <si>
+    <t>The gene expressions sequence read count</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>categorical</t>
+  </si>
+  <si>
+    <t>The gene expressions sequence read per million microRNA ratio</t>
+  </si>
+  <si>
+    <t>Does the gene have cross map overlap</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -194,6 +301,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -376,7 +498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -491,6 +613,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -536,8 +667,28 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -892,7 +1043,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD31151-FCF5-3A49-AEA2-4DC459D3C9B6}">
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD7CA80-EFDF-304C-9DE9-C9180EBC297F}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="84" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
